--- a/Docs/平衡测算文档.xlsx
+++ b/Docs/平衡测算文档.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Warhummer III AdamWorkshop\MyMods\商队Rogue玩法Mod\TotalWarIIIMod-RogueTheWarHammer\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5769DA90-DFE4-4391-B176-B84BFCE3FDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2A41E5-FADF-4B41-BE6F-DA69D6DB95BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -135,7 +135,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>调权</t>
+    <t>拆分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1535,6 +1535,9 @@
       <c r="H9" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="I9" s="1">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1558,12 +1561,12 @@
         <v>5200</v>
       </c>
       <c r="H10" s="1">
-        <f>$I$2+0.8*(D10-$I$2)</f>
-        <v>4900</v>
+        <f>D10*(1-I$9)</f>
+        <v>3349.9999999999995</v>
       </c>
       <c r="I10" s="1">
-        <f>$I$2+1.25*(D10-$I$2)</f>
-        <v>5125</v>
+        <f>D10-H10</f>
+        <v>1650.0000000000005</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -1587,12 +1590,12 @@
         <v>5900</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" ref="H11:H44" si="1">$I$2+0.8*(D11-$I$2)</f>
-        <v>5300</v>
+        <f t="shared" ref="H11:H47" si="1">D11*(1-I$9)</f>
+        <v>3684.9999999999995</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" ref="I11:I44" si="2">$I$2+1.25*(D11-$I$2)</f>
-        <v>5750</v>
+        <f t="shared" ref="I11:I47" si="2">D11-H11</f>
+        <v>1815.0000000000005</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -1617,11 +1620,11 @@
       </c>
       <c r="H12" s="1">
         <f t="shared" si="1"/>
-        <v>5700</v>
+        <v>4019.9999999999995</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" si="2"/>
-        <v>6375</v>
+        <v>1980.0000000000005</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1646,11 +1649,11 @@
       </c>
       <c r="H13" s="1">
         <f t="shared" si="1"/>
-        <v>6100</v>
+        <v>4354.9999999999991</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="2"/>
-        <v>7000</v>
+        <v>2145.0000000000009</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1679,11 +1682,11 @@
       </c>
       <c r="H14" s="1">
         <f t="shared" si="1"/>
-        <v>6500</v>
+        <v>4689.9999999999991</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="2"/>
-        <v>7625</v>
+        <v>2310.0000000000009</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1708,11 +1711,11 @@
       </c>
       <c r="H15" s="1">
         <f t="shared" si="1"/>
-        <v>7180</v>
+        <v>5259.4999999999991</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="2"/>
-        <v>8687.5</v>
+        <v>2590.5000000000009</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -1737,11 +1740,11 @@
       </c>
       <c r="H16" s="1">
         <f t="shared" si="1"/>
-        <v>7860</v>
+        <v>5828.9999999999991</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="2"/>
-        <v>9750</v>
+        <v>2871.0000000000009</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1766,11 +1769,11 @@
       </c>
       <c r="H17" s="1">
         <f t="shared" si="1"/>
-        <v>8540</v>
+        <v>6398.4999999999991</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="2"/>
-        <v>10812.5</v>
+        <v>3151.5000000000009</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1795,11 +1798,11 @@
       </c>
       <c r="H18" s="1">
         <f t="shared" si="1"/>
-        <v>9220</v>
+        <v>6967.9999999999991</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="2"/>
-        <v>11875</v>
+        <v>3432.0000000000009</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1828,11 +1831,11 @@
       </c>
       <c r="H19" s="1">
         <f t="shared" si="1"/>
-        <v>9900</v>
+        <v>7537.4999999999991</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="2"/>
-        <v>12937.5</v>
+        <v>3712.5000000000009</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1857,11 +1860,11 @@
       </c>
       <c r="H20" s="1">
         <f t="shared" si="1"/>
-        <v>10780</v>
+        <v>8274.5</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="2"/>
-        <v>14312.5</v>
+        <v>4075.5</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1886,11 +1889,11 @@
       </c>
       <c r="H21" s="1">
         <f t="shared" si="1"/>
-        <v>11660</v>
+        <v>9011.4999999999982</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="2"/>
-        <v>15687.5</v>
+        <v>4438.5000000000018</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1915,11 +1918,11 @@
       </c>
       <c r="H22" s="1">
         <f t="shared" si="1"/>
-        <v>12540</v>
+        <v>9748.4999999999982</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="2"/>
-        <v>17062.5</v>
+        <v>4801.5000000000018</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1944,11 +1947,11 @@
       </c>
       <c r="H23" s="1">
         <f t="shared" si="1"/>
-        <v>13420</v>
+        <v>10485.499999999998</v>
       </c>
       <c r="I23" s="1">
         <f t="shared" si="2"/>
-        <v>18437.5</v>
+        <v>5164.5000000000018</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1977,11 +1980,11 @@
       </c>
       <c r="H24" s="1">
         <f t="shared" si="1"/>
-        <v>14300</v>
+        <v>11222.499999999998</v>
       </c>
       <c r="I24" s="1">
         <f t="shared" si="2"/>
-        <v>19812.5</v>
+        <v>5527.5000000000018</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -2006,11 +2009,11 @@
       </c>
       <c r="H25" s="1">
         <f t="shared" si="1"/>
-        <v>15260</v>
+        <v>12026.499999999998</v>
       </c>
       <c r="I25" s="1">
         <f t="shared" si="2"/>
-        <v>21312.5</v>
+        <v>5923.5000000000018</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -2035,11 +2038,11 @@
       </c>
       <c r="H26" s="1">
         <f t="shared" si="1"/>
-        <v>16220</v>
+        <v>12830.499999999998</v>
       </c>
       <c r="I26" s="1">
         <f t="shared" si="2"/>
-        <v>22812.5</v>
+        <v>6319.5000000000018</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -2064,11 +2067,11 @@
       </c>
       <c r="H27" s="1">
         <f t="shared" si="1"/>
-        <v>17180</v>
+        <v>13634.499999999998</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" si="2"/>
-        <v>24312.5</v>
+        <v>6715.5000000000018</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -2093,11 +2096,11 @@
       </c>
       <c r="H28" s="1">
         <f t="shared" si="1"/>
-        <v>18140</v>
+        <v>14438.499999999998</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" si="2"/>
-        <v>25812.5</v>
+        <v>7111.5000000000018</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -2126,11 +2129,11 @@
       </c>
       <c r="H29" s="1">
         <f t="shared" si="1"/>
-        <v>19100</v>
+        <v>15242.499999999998</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" si="2"/>
-        <v>27312.5</v>
+        <v>7507.5000000000018</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -2155,11 +2158,11 @@
       </c>
       <c r="H30" s="1">
         <f t="shared" si="1"/>
-        <v>20060</v>
+        <v>16046.499999999998</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" si="2"/>
-        <v>28812.5</v>
+        <v>7903.5000000000018</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -2184,11 +2187,11 @@
       </c>
       <c r="H31" s="1">
         <f t="shared" si="1"/>
-        <v>21020</v>
+        <v>16850.5</v>
       </c>
       <c r="I31" s="1">
         <f t="shared" si="2"/>
-        <v>30312.5</v>
+        <v>8299.5</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -2213,11 +2216,11 @@
       </c>
       <c r="H32" s="1">
         <f t="shared" si="1"/>
-        <v>21980</v>
+        <v>17654.499999999996</v>
       </c>
       <c r="I32" s="1">
         <f t="shared" si="2"/>
-        <v>31812.5</v>
+        <v>8695.5000000000036</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -2242,11 +2245,11 @@
       </c>
       <c r="H33" s="1">
         <f t="shared" si="1"/>
-        <v>22940</v>
+        <v>18458.499999999996</v>
       </c>
       <c r="I33" s="1">
         <f t="shared" si="2"/>
-        <v>33312.5</v>
+        <v>9091.5000000000036</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -2275,11 +2278,11 @@
       </c>
       <c r="H34" s="1">
         <f t="shared" si="1"/>
-        <v>23900</v>
+        <v>19262.499999999996</v>
       </c>
       <c r="I34" s="1">
         <f t="shared" si="2"/>
-        <v>34812.5</v>
+        <v>9487.5000000000036</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -2304,11 +2307,11 @@
       </c>
       <c r="H35" s="1">
         <f t="shared" si="1"/>
-        <v>24860</v>
+        <v>20066.499999999996</v>
       </c>
       <c r="I35" s="1">
         <f t="shared" si="2"/>
-        <v>36312.5</v>
+        <v>9883.5000000000036</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -2333,11 +2336,11 @@
       </c>
       <c r="H36" s="1">
         <f t="shared" si="1"/>
-        <v>25820</v>
+        <v>20870.499999999996</v>
       </c>
       <c r="I36" s="1">
         <f t="shared" si="2"/>
-        <v>37812.5</v>
+        <v>10279.500000000004</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -2362,11 +2365,11 @@
       </c>
       <c r="H37" s="1">
         <f t="shared" si="1"/>
-        <v>26780</v>
+        <v>21674.499999999996</v>
       </c>
       <c r="I37" s="1">
         <f t="shared" si="2"/>
-        <v>39312.5</v>
+        <v>10675.500000000004</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2391,11 +2394,11 @@
       </c>
       <c r="H38" s="1">
         <f t="shared" si="1"/>
-        <v>27740</v>
+        <v>22478.499999999996</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" si="2"/>
-        <v>40812.5</v>
+        <v>11071.500000000004</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2424,11 +2427,11 @@
       </c>
       <c r="H39" s="1">
         <f t="shared" si="1"/>
-        <v>28700</v>
+        <v>23282.499999999996</v>
       </c>
       <c r="I39" s="1">
         <f t="shared" si="2"/>
-        <v>42312.5</v>
+        <v>11467.500000000004</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2453,11 +2456,11 @@
       </c>
       <c r="H40" s="1">
         <f t="shared" si="1"/>
-        <v>29820</v>
+        <v>24220.499999999996</v>
       </c>
       <c r="I40" s="1">
         <f t="shared" si="2"/>
-        <v>44062.5</v>
+        <v>11929.500000000004</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -2482,11 +2485,11 @@
       </c>
       <c r="H41" s="1">
         <f t="shared" si="1"/>
-        <v>30940</v>
+        <v>25158.499999999996</v>
       </c>
       <c r="I41" s="1">
         <f t="shared" si="2"/>
-        <v>45812.5</v>
+        <v>12391.500000000004</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2511,11 +2514,11 @@
       </c>
       <c r="H42" s="1">
         <f t="shared" si="1"/>
-        <v>32060</v>
+        <v>26096.499999999996</v>
       </c>
       <c r="I42" s="1">
         <f t="shared" si="2"/>
-        <v>47562.5</v>
+        <v>12853.500000000004</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -2540,11 +2543,11 @@
       </c>
       <c r="H43" s="1">
         <f t="shared" si="1"/>
-        <v>33180</v>
+        <v>27034.499999999996</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="2"/>
-        <v>49312.5</v>
+        <v>13315.500000000004</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -2569,11 +2572,11 @@
       </c>
       <c r="H44" s="1">
         <f t="shared" si="1"/>
-        <v>34300</v>
+        <v>27972.499999999996</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" si="2"/>
-        <v>51062.5</v>
+        <v>13777.500000000004</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -2584,6 +2587,14 @@
         <f t="shared" si="22"/>
         <v>43150</v>
       </c>
+      <c r="H45" s="1">
+        <f t="shared" si="1"/>
+        <v>28910.499999999996</v>
+      </c>
+      <c r="I45" s="1">
+        <f t="shared" si="2"/>
+        <v>14239.500000000004</v>
+      </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
@@ -2593,6 +2604,14 @@
         <f t="shared" si="22"/>
         <v>44550</v>
       </c>
+      <c r="H46" s="1">
+        <f t="shared" si="1"/>
+        <v>29848.499999999996</v>
+      </c>
+      <c r="I46" s="1">
+        <f t="shared" si="2"/>
+        <v>14701.500000000004</v>
+      </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
@@ -2601,6 +2620,14 @@
       <c r="D47" s="1">
         <f t="shared" si="22"/>
         <v>45950</v>
+      </c>
+      <c r="H47" s="1">
+        <f t="shared" si="1"/>
+        <v>30786.499999999996</v>
+      </c>
+      <c r="I47" s="1">
+        <f t="shared" si="2"/>
+        <v>15163.500000000004</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/平衡测算文档.xlsx
+++ b/Docs/平衡测算文档.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Warhummer III AdamWorkshop\MyMods\商队Rogue玩法Mod\TotalWarIIIMod-RogueTheWarHammer\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2A41E5-FADF-4B41-BE6F-DA69D6DB95BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247F3177-5BCC-4E31-ADBE-479425935795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2400" windowWidth="30720" windowHeight="14160" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Docs/平衡测算文档.xlsx
+++ b/Docs/平衡测算文档.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Warhummer III AdamWorkshop\MyMods\商队Rogue玩法Mod\TotalWarIIIMod-RogueTheWarHammer\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247F3177-5BCC-4E31-ADBE-479425935795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC943D2-5616-4BBF-A1A7-0760DB0E233B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2400" windowWidth="30720" windowHeight="14160" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
